--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.396667370975091</v>
+        <v>1.201958447783452</v>
       </c>
       <c r="D2" t="n">
-        <v>8.062257748298549</v>
+        <v>1.310116884098514</v>
       </c>
       <c r="E2" t="n">
-        <v>11.12461077809407</v>
+        <v>1.807749251440286</v>
       </c>
       <c r="F2" t="n">
-        <v>11.25983298250152</v>
+        <v>1.829722859656498</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.51828004823061</v>
+        <v>5.609220507837474</v>
       </c>
       <c r="D3" t="n">
-        <v>35.62980782181921</v>
+        <v>5.789843771045621</v>
       </c>
       <c r="E3" t="n">
-        <v>11.12461077809407</v>
+        <v>1.807749251440286</v>
       </c>
       <c r="F3" t="n">
-        <v>11.25983298250152</v>
+        <v>1.829722859656498</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.24219178347752</v>
+        <v>3.776856164815097</v>
       </c>
       <c r="D4" t="n">
-        <v>22.58759315359258</v>
+        <v>3.670483887458794</v>
       </c>
       <c r="E4" t="n">
-        <v>11.12461077809407</v>
+        <v>1.807749251440286</v>
       </c>
       <c r="F4" t="n">
-        <v>11.25983298250152</v>
+        <v>1.829722859656498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
